--- a/business-analysis/stakeholder-analysis.xlsx
+++ b/business-analysis/stakeholder-analysis.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stakeholder Register" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power-Interest Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stakeholder Register'!$A$4:$F$13</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +55,14 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -91,8 +99,18 @@
         <fgColor rgb="009DC3E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -114,11 +132,72 @@
         <color rgb="00B7B7B7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7B7B7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7B7B7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,6 +233,30 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -539,10 +642,15 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Simulated for this portfolio case study — no real stakeholder interviews were conducted. Stakeholders represent realistic roles for an FMCG retailer of RetailCo's profile.</t>
+          <t>This is an independent portfolio case study. No real stakeholder interviews were conducted. Stakeholder roles, interests, influence levels, needs and engagement approaches are simulated for BA practice.
+• Stakeholder classifications are simulated assumptions.
+• No real stakeholder meetings occurred.
+• Stakeholder information is not presented as real organizational evidence.
+• Supplier/lead-time involvement is a hypothesis consideration, not proof of a root cause.
+• Proposed workshops, validation and UAT activities are simulated BA activities.</t>
         </is>
       </c>
     </row>
@@ -586,7 +694,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Simulated executive sponsor for the reporting/decision-support initiative</t>
+          <t>Simulated executive sponsor responsible for business objectives and overall direction</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -601,12 +709,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Executive summary of revenue, margin, and inventory-risk KPIs; ROI/business case for the proposed solution</t>
+          <t>Executive KPIs, business priorities, solution options, business-case considerations</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Steering-level updates at project milestones; sign-off on scope, business requirements, and final recommendation</t>
+          <t>Validate scope, objectives, key requirements and final recommendation</t>
         </is>
       </c>
     </row>
@@ -618,7 +726,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Owns revenue performance across category, brand, city, and channel</t>
+          <t>Simulated owner of sales performance and commercial reporting</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -633,12 +741,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Revenue and unit trends by category, brand, city, store format, and channel</t>
+          <t>Revenue, units sold and margin by category, brand, city, store format and channel</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Requirements workshops; validates sales KPI definitions and dashboard Page 2 (Sales Performance)</t>
+          <t>Validate business questions, KPI requirements and reporting needs</t>
         </is>
       </c>
     </row>
@@ -650,7 +758,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Owns stock monitoring and reorder decisions</t>
+          <t>Simulated owner of inventory monitoring and replenishment</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -665,12 +773,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Transactions recorded below reorder level, by category and city; lead-time context</t>
+          <t>Inventory exceptions, including transactions below reorder level, and replenishment-related information</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Requirements workshops for inventory-monitoring features; primary reviewer for dashboard Page 4 and UAT</t>
+          <t>Validate inventory requirements, business rules, process needs and UAT scenarios</t>
         </is>
       </c>
     </row>
@@ -682,7 +790,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Owns margin/profitability accuracy and reporting integrity</t>
+          <t>Simulated owner of financial reporting and profitability analysis</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -697,12 +805,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Margin and margin % by category/brand; validation of revenue-cost-margin calculation logic</t>
+          <t>Revenue, cost and margin definitions and calculations</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Validates KPI formulas and margin-related business rules; reviews BRD financial sections</t>
+          <t>Validate KPI definitions, formulas and financial business rules</t>
         </is>
       </c>
     </row>
@@ -714,7 +822,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Oversees store-format and channel operating efficiency</t>
+          <t>Simulated owner of operational performance across stores and channels</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -729,12 +837,12 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Store format and channel performance comparisons</t>
+          <t>Store/channel performance and operational exception information</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Consulted during As-Is/To-Be process design; reviews process pain points</t>
+          <t>Contribute to process modelling, operational requirements and simulated pain-point analysis</t>
         </is>
       </c>
     </row>
@@ -746,12 +854,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Manages supplier relationships and lead time</t>
+          <t>Simulated procurement and supplier-management role</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Medium-High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -761,12 +869,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Lead-time analysis and its relationship to below-reorder-level transactions</t>
+          <t>Supplier and lead-time information where relevant to inventory hypotheses</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Consulted for inventory-related functional requirements; reviews reorder/lead-time KPI definitions</t>
+          <t>Consult when evaluating supplier or lead-time-related hypotheses; do not assume lead time is a root cause</t>
         </is>
       </c>
     </row>
@@ -778,7 +886,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Represents store-level, day-to-day performance visibility</t>
+          <t>Simulated day-to-day operational and reporting user</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -793,12 +901,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>City/store-level KPI views; simple, fast dashboard access</t>
+          <t>Actionable sales and inventory exceptions relevant to store operations</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Consulted for usability/NFRs and included in UAT as an end-user representative</t>
+          <t>Provide simulated end-user needs and usability considerations for reporting/UAT</t>
         </is>
       </c>
     </row>
@@ -810,7 +918,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Simulated technical partner responsible for data quality and KPI build</t>
+          <t>Simulated technical and data-analysis role</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -825,12 +933,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Data dictionary, data-quality findings, and KPI formula definitions</t>
+          <t>Data definitions, data quality findings, KPI formulas and reporting logic</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Works directly with the BA on data validation, SQL/Excel analysis, and dashboard build feasibility</t>
+          <t>Support data validation, KPI definitions, analysis and reporting requirements</t>
         </is>
       </c>
     </row>
@@ -842,12 +950,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Oversees data access, security, and technical feasibility</t>
+          <t>Simulated technical stakeholder responsible for system considerations</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Low-Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -857,16 +965,17 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Non-functional requirements: security, availability, data access needs</t>
+          <t>Security, access, technical constraints, feasibility and non-functional requirements</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Reviews NFRs and technical constraints; consulted on solution-option feasibility</t>
+          <t>Review non-functional requirements and solution feasibility considerations</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:F13"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
@@ -881,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -890,6 +999,8 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -900,26 +1011,33 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Positions are illustrative, based on each simulated role's typical scope of authority and stake in this project.</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Positions are illustrative, based on each simulated role's typical scope of authority and stake in this project. Procurement Manager is kept at Medium Power / Medium Interest rather than forced into a High/Low quadrant.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="7" t="inlineStr">
+      <c r="A4" s="20" t="n"/>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>LOW INTEREST</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>MEDIUM INTEREST</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>HIGH INTEREST</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>HIGH POWER</t>
         </is>
@@ -931,7 +1049,8 @@
 IT Representative</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="23" t="n"/>
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>MANAGE CLOSELY
 Business Sponsor
@@ -945,80 +1064,130 @@
     <row r="7" ht="20" customHeight="1"/>
     <row r="8" ht="20" customHeight="1"/>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>MEDIUM POWER</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="n"/>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>CONSULT
+Procurement Manager
+(supplier/lead-time hypotheses only)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1"/>
+    <row r="11" ht="20" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>LOW POWER</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>MONITOR
 (No stakeholders currently mapped to this quadrant)</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E12" s="23" t="n"/>
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>KEEP INFORMED
 Store Manager
-BI / Data Analyst
-Procurement Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1"/>
-    <row r="11" ht="20" customHeight="1"/>
-    <row r="12" ht="20" customHeight="1"/>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+BI / Data Analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1"/>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>Engagement strategy by quadrant:</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>• Manage Closely — highest priority. Direct involvement in requirements workshops, regular check-ins, sign-off authority on deliverables.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>• Keep Satisfied — consulted at key decision points; summarized updates rather than full workshop involvement.</t>
-        </is>
-      </c>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>• Keep Informed — kept up to date via demos/UAT participation; input welcomed but not decision-driving.</t>
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>• Manage Closely (High Power / High Interest) — involve in scope, requirements, KPI decisions and recommendation validation.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>• Monitor — no active engagement required beyond awareness; re-assess if their interest or influence changes.</t>
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>• Keep Satisfied (High Power / Low Interest) — provide relevant updates and involve when operational or technical decisions require input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>• Consult (Medium Power / Medium Interest) — consult when supplier or lead-time information is relevant; do not assume it is a confirmed root cause.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>• Keep Informed (Low Power / High Interest) — keep informed and involved in requirements, usability, data definitions and validation activities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>• Monitor (Low Power / Low Interest) — no stakeholders currently identified.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A9:B12"/>
+  <mergeCells count="22">
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A12:B15"/>
+    <mergeCell ref="E12:F15"/>
+    <mergeCell ref="C12:D15"/>
+    <mergeCell ref="G12:H15"/>
+    <mergeCell ref="C9:D11"/>
+    <mergeCell ref="A9:B11"/>
+    <mergeCell ref="E9:F11"/>
+    <mergeCell ref="C5:D8"/>
+    <mergeCell ref="G5:H8"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E9:F12"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A5:B8"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="E5:F8"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C9:D12"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="C5:D8"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="G9:H11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
